--- a/datasets/edge_cases.xlsx
+++ b/datasets/edge_cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,38 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>ID Alias</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Func 1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Func 2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>Func 3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Pool</t>
+          <t>Func 4</t>
         </is>
       </c>
     </row>
@@ -464,10 +447,8 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Employee 1</t>
-        </is>
+      <c r="B2" t="b">
+        <v>0</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -476,9 +457,6 @@
         <v>0</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -486,10 +464,8 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Employee 2</t>
-        </is>
+      <c r="B3" t="b">
+        <v>0</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -498,9 +474,6 @@
         <v>0</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -508,10 +481,8 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Employee 3</t>
-        </is>
+      <c r="B4" t="b">
+        <v>1</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -520,9 +491,6 @@
         <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -530,10 +498,8 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Employee 4</t>
-        </is>
+      <c r="B5" t="b">
+        <v>1</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -542,9 +508,6 @@
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -552,21 +515,16 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Employee 5</t>
-        </is>
+      <c r="B6" t="b">
+        <v>1</v>
       </c>
       <c r="C6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -574,21 +532,16 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Employee 6</t>
-        </is>
+      <c r="B7" t="b">
+        <v>0</v>
       </c>
       <c r="C7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -596,21 +549,16 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Employee 7</t>
-        </is>
+      <c r="B8" t="b">
+        <v>0</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -618,10 +566,8 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Employee 8</t>
-        </is>
+      <c r="B9" t="b">
+        <v>0</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
@@ -630,9 +576,6 @@
         <v>0</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -640,10 +583,8 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Employee 9</t>
-        </is>
+      <c r="B10" t="b">
+        <v>0</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
@@ -652,9 +593,6 @@
         <v>0</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -662,10 +600,8 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Employee 10</t>
-        </is>
+      <c r="B11" t="b">
+        <v>0</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -674,9 +610,6 @@
         <v>0</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -684,10 +617,8 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Employee 11</t>
-        </is>
+      <c r="B12" t="b">
+        <v>0</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -696,9 +627,6 @@
         <v>0</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -706,10 +634,8 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Employee 12</t>
-        </is>
+      <c r="B13" t="b">
+        <v>0</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
@@ -718,9 +644,6 @@
         <v>0</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -728,10 +651,8 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Employee 13</t>
-        </is>
+      <c r="B14" t="b">
+        <v>0</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -740,9 +661,6 @@
         <v>0</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -750,10 +668,8 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Employee 14</t>
-        </is>
+      <c r="B15" t="b">
+        <v>0</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -762,9 +678,6 @@
         <v>0</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -772,10 +685,8 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Employee 15</t>
-        </is>
+      <c r="B16" t="b">
+        <v>0</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -784,9 +695,6 @@
         <v>0</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>
